--- a/mlef_pipeline/results/OS_6/SQUAMOUS/RWD_FMRAD/results.xlsx
+++ b/mlef_pipeline/results/OS_6/SQUAMOUS/RWD_FMRAD/results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,26 +468,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.74 ± 0.08</t>
+          <t>0.80 ± 0.07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.59 ± 0.07</t>
+          <t>0.70 ± 0.08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.53 ± 0.07</t>
+          <t>0.72 ± 0.17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.75 ± 0.15</t>
+          <t>0.73 ± 0.11</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>139</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3">
@@ -498,26 +498,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.72 ± 0.22</t>
+          <t>0.54 ± 0.25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -528,26 +528,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.64 ± 0.35</t>
+          <t>0.34 ± 0.44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/mlef_pipeline/results/OS_6/SQUAMOUS/RWD_FMRAD/results.xlsx
+++ b/mlef_pipeline/results/OS_6/SQUAMOUS/RWD_FMRAD/results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
